--- a/rules/CORE-000743/negative/01/data/unit-test-coreid-FB0918-negative.xlsx
+++ b/rules/CORE-000743/negative/01/data/unit-test-coreid-FB0918-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ti.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ti.xpt" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +46,7 @@
       <sz val="7"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +75,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +142,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,7 +591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +623,342 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Has disease under study</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>INCL01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Age 21 or greater</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>INCL01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pregnant or lactating</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EXCL01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Has disease under study</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>INCL01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Age 18 or greater</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>INCL02A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IETEST</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pregnant or lactating</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ti.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IETESTCD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>INCL02A</t>
         </is>
       </c>
     </row>
@@ -758,12 +1103,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>INCL01</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Has disease under study</t>
         </is>
@@ -788,12 +1133,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>INCL01</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Age 21 or greater</t>
         </is>
@@ -818,12 +1163,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>EXCL01</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Pregnant or lactating</t>
         </is>
@@ -848,12 +1193,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>INCL01</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Has disease under study</t>
         </is>
@@ -878,12 +1223,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>INCL02A</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Age 18 or greater</t>
         </is>
@@ -908,8 +1253,12 @@
           <t>TI</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>INCL02A</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Pregnant or lactating</t>
         </is>
